--- a/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/08_it_budget_spend_value.xlsx
+++ b/datasets/tenant-inputs/generated/harbortrust-bank/standard-2026-07-v3/core-dimensions/08_it_budget_spend_value.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rf4eb11b6c3df47ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Rf957ac954af3415f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R36bbad3f12794d9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rfd408e7e57ab4476"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R345abd1a134e4a05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="Rcc87ff0ab31943e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tower Views" sheetId="7" r:id="Rb994974de5904141"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="R9d404c7dfd8e4288"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="Rafb203b971e74e31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R3aebf06aed2a4cce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="Rd58d9d4bfb1b4b4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R9d3b59f3880547e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R535c55b8177c4905"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tower Views" sheetId="7" r:id="R4f6fc4e7aa204e09"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -640,7 +640,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R310b5af97e244f46"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c0eee49e435465a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -821,7 +821,7 @@
         <x:v>Chief Strategy Officer</x:v>
       </x:c>
       <x:c r="O6" s="78" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Validate Executive Office run spend baseline (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for it budget spend value.</x:v>
       </x:c>
       <x:c r="P6" s="41" t="str">
         <x:v>Medium</x:v>
@@ -871,7 +871,7 @@
         <x:v>Chief Strategy Officer</x:v>
       </x:c>
       <x:c r="O7" s="79" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Confirm Enterprise profile and corporate priorities change / modernization budget (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this it budget spend value record is used downstream.</x:v>
       </x:c>
       <x:c r="P7" s="45" t="str">
         <x:v>Medium</x:v>
@@ -921,7 +921,7 @@
         <x:v>Retail Banking COO</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Attach client evidence for Retail Deposits and Branch Operations run spend baseline (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P8" t="str">
         <x:v>Medium</x:v>
@@ -971,7 +971,7 @@
         <x:v>Retail Banking COO</x:v>
       </x:c>
       <x:c r="O9" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Reconcile Retail banking change / modernization budget (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P9" t="str">
         <x:v>Medium</x:v>
@@ -1021,7 +1021,7 @@
         <x:v>Commercial Banking COO</x:v>
       </x:c>
       <x:c r="O10" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Commercial Lending and Treasury run spend baseline (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P10" t="str">
         <x:v>Medium</x:v>
@@ -1071,7 +1071,7 @@
         <x:v>Commercial Banking COO</x:v>
       </x:c>
       <x:c r="O11" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Validate Commercial banking change / modernization budget (record 6) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for it budget spend value.</x:v>
       </x:c>
       <x:c r="P11" t="str">
         <x:v>Medium</x:v>
@@ -1121,7 +1121,7 @@
         <x:v>Head of Cards</x:v>
       </x:c>
       <x:c r="O12" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Confirm Cards Operations run spend baseline (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this it budget spend value record is used downstream.</x:v>
       </x:c>
       <x:c r="P12" t="str">
         <x:v>Medium</x:v>
@@ -1171,7 +1171,7 @@
         <x:v>Head of Cards</x:v>
       </x:c>
       <x:c r="O13" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Attach client evidence for Cards change / modernization budget (record 8), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P13" t="str">
         <x:v>Medium</x:v>
@@ -1221,7 +1221,7 @@
         <x:v>Payments Leader</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Reconcile Payments Operations run spend baseline (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P14" t="str">
         <x:v>Medium</x:v>
@@ -1271,7 +1271,7 @@
         <x:v>Payments Leader</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Payments change / modernization budget (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P15" t="str">
         <x:v>Medium</x:v>
@@ -1321,7 +1321,7 @@
         <x:v>Head of Consumer Lending</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Validate Consumer Lending Operations run spend baseline (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for it budget spend value.</x:v>
       </x:c>
       <x:c r="P16" t="str">
         <x:v>Medium</x:v>
@@ -1371,7 +1371,7 @@
         <x:v>Head of Consumer Lending</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Confirm Lending change / modernization budget (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this it budget spend value record is used downstream.</x:v>
       </x:c>
       <x:c r="P17" t="str">
         <x:v>Medium</x:v>
@@ -1421,7 +1421,7 @@
         <x:v>Head of Wealth</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Attach client evidence for Wealth Advisory and Brokerage run spend baseline (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P18" t="str">
         <x:v>Medium</x:v>
@@ -1471,7 +1471,7 @@
         <x:v>Head of Wealth</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Reconcile Wealth change / modernization budget (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P19" t="str">
         <x:v>Medium</x:v>
@@ -1521,7 +1521,7 @@
         <x:v>CRO</x:v>
       </x:c>
       <x:c r="O20" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Validate Fraud and Risk Operations run spend baseline (record 15) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P20" t="str">
         <x:v>Medium</x:v>
@@ -1571,7 +1571,7 @@
         <x:v>CRO</x:v>
       </x:c>
       <x:c r="O21" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Validate Fraud / risk change / modernization budget (record 16) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P21" t="str">
         <x:v>Medium</x:v>
@@ -1621,7 +1621,7 @@
         <x:v>Chief Compliance Officer</x:v>
       </x:c>
       <x:c r="O22" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Confirm Compliance and Model Risk Management run spend baseline (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this it budget spend value record is used downstream.</x:v>
       </x:c>
       <x:c r="P22" t="str">
         <x:v>Medium</x:v>
@@ -1671,7 +1671,7 @@
         <x:v>Chief Compliance Officer</x:v>
       </x:c>
       <x:c r="O23" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Attach client evidence for Compliance / model risk change / modernization budget (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P23" t="str">
         <x:v>Medium</x:v>
@@ -1721,7 +1721,7 @@
         <x:v>Chief Experience Officer</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Reconcile Contact Center and Servicing run spend baseline (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P24" t="str">
         <x:v>Medium</x:v>
@@ -1771,7 +1771,7 @@
         <x:v>Chief Experience Officer</x:v>
       </x:c>
       <x:c r="O25" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Contact center change / modernization budget (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P25" t="str">
         <x:v>Medium</x:v>
@@ -1821,7 +1821,7 @@
         <x:v>Digital Banking Product Owner</x:v>
       </x:c>
       <x:c r="O26" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Validate Digital Account Opening and Onboarding run spend baseline (record 21) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for it budget spend value.</x:v>
       </x:c>
       <x:c r="P26" t="str">
         <x:v>Medium</x:v>
@@ -1871,7 +1871,7 @@
         <x:v>Digital Banking Product Owner</x:v>
       </x:c>
       <x:c r="O27" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Confirm Digital onboarding change / modernization budget (record 22) current-vs-target status, module boundary, volume baseline, and relationship links before this it budget spend value record is used downstream.</x:v>
       </x:c>
       <x:c r="P27" t="str">
         <x:v>Medium</x:v>
@@ -1921,7 +1921,7 @@
         <x:v>CIO</x:v>
       </x:c>
       <x:c r="O28" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Attach client evidence for Core Banking Modernization run spend baseline (record 23), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P28" t="str">
         <x:v>Medium</x:v>
@@ -1971,7 +1971,7 @@
         <x:v>CIO</x:v>
       </x:c>
       <x:c r="O29" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Reconcile Core banking modernization change / modernization budget (record 24) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P29" t="str">
         <x:v>Medium</x:v>
@@ -2021,7 +2021,7 @@
         <x:v>CDAO</x:v>
       </x:c>
       <x:c r="O30" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Customer 360 Data Product run spend baseline (record 25) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P30" t="str">
         <x:v>Medium</x:v>
@@ -2071,7 +2071,7 @@
         <x:v>CDAO</x:v>
       </x:c>
       <x:c r="O31" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Validate Customer 360 change / modernization budget (record 26) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for it budget spend value.</x:v>
       </x:c>
       <x:c r="P31" t="str">
         <x:v>Medium</x:v>
@@ -2121,7 +2121,7 @@
         <x:v>Retail Analytics Lead</x:v>
       </x:c>
       <x:c r="O32" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Confirm Retail Banking Analytics run spend baseline (record 27) current-vs-target status, module boundary, volume baseline, and relationship links before this it budget spend value record is used downstream.</x:v>
       </x:c>
       <x:c r="P32" t="str">
         <x:v>Medium</x:v>
@@ -2171,7 +2171,7 @@
         <x:v>Retail Analytics Lead</x:v>
       </x:c>
       <x:c r="O33" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Attach client evidence for Retail banking analytics change / modernization budget (record 28), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P33" t="str">
         <x:v>Medium</x:v>
@@ -2221,7 +2221,7 @@
         <x:v>Cards Analytics Lead</x:v>
       </x:c>
       <x:c r="O34" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Reconcile Cards Portfolio Analytics run spend baseline (record 29) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P34" t="str">
         <x:v>Medium</x:v>
@@ -2271,7 +2271,7 @@
         <x:v>Cards Analytics Lead</x:v>
       </x:c>
       <x:c r="O35" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cards analytics change / modernization budget (record 30) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P35" t="str">
         <x:v>Medium</x:v>
@@ -2321,7 +2321,7 @@
         <x:v>Payments Analytics Lead</x:v>
       </x:c>
       <x:c r="O36" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Validate Payments and Settlement Analytics run spend baseline (record 31) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for it budget spend value.</x:v>
       </x:c>
       <x:c r="P36" t="str">
         <x:v>Medium</x:v>
@@ -2371,7 +2371,7 @@
         <x:v>Payments Analytics Lead</x:v>
       </x:c>
       <x:c r="O37" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Confirm Payments analytics change / modernization budget (record 32) current-vs-target status, module boundary, volume baseline, and relationship links before this it budget spend value record is used downstream.</x:v>
       </x:c>
       <x:c r="P37" t="str">
         <x:v>Medium</x:v>
@@ -2421,7 +2421,7 @@
         <x:v>Fraud Analytics Lead</x:v>
       </x:c>
       <x:c r="O38" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Validate Fraud and Risk Analytics run spend baseline (record 33) against Fraud Analyst Copilot evidence: queue aging mixed with model quality signals; confirm model-risk-approved evaluation set owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P38" t="str">
         <x:v>Medium</x:v>
@@ -2471,7 +2471,7 @@
         <x:v>Fraud Analytics Lead</x:v>
       </x:c>
       <x:c r="O39" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Validate Fraud/risk analytics change / modernization budget (record 34) against Fraud Analyst Copilot evidence: case outcome feedback gaps; confirm fraud analyst copilot with cited case packet owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P39" t="str">
         <x:v>Medium</x:v>
@@ -2521,7 +2521,7 @@
         <x:v>CDAO</x:v>
       </x:c>
       <x:c r="O40" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Cloud Data Platform run spend baseline (record 35) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P40" t="str">
         <x:v>Medium</x:v>
@@ -2571,7 +2571,7 @@
         <x:v>CDAO</x:v>
       </x:c>
       <x:c r="O41" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Validate Enterprise data platform / cloud data foundation change / modernization budget (record 36) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for it budget spend value.</x:v>
       </x:c>
       <x:c r="P41" t="str">
         <x:v>Medium</x:v>
@@ -2621,7 +2621,7 @@
         <x:v>CIO / CFO</x:v>
       </x:c>
       <x:c r="O42" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Confirm IT Budget and Tower Baseline run spend baseline (record 37) current-vs-target status, module boundary, volume baseline, and relationship links before this it budget spend value record is used downstream.</x:v>
       </x:c>
       <x:c r="P42" t="str">
         <x:v>Medium</x:v>
@@ -2671,7 +2671,7 @@
         <x:v>CIO / CFO</x:v>
       </x:c>
       <x:c r="O43" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Attach client evidence for IT budget and Tower spend baseline change / modernization budget (record 38), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P43" t="str">
         <x:v>Medium</x:v>
@@ -2721,7 +2721,7 @@
         <x:v>Chief Procurement Officer</x:v>
       </x:c>
       <x:c r="O44" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Reconcile Vendor and Contract Optimization run spend baseline (record 39) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P44" t="str">
         <x:v>Medium</x:v>
@@ -2771,7 +2771,7 @@
         <x:v>Chief Procurement Officer</x:v>
       </x:c>
       <x:c r="O45" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Vendor / contract / sourcing context change / modernization budget (record 40) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P45" t="str">
         <x:v>Medium</x:v>
@@ -2821,7 +2821,7 @@
         <x:v>CTO</x:v>
       </x:c>
       <x:c r="O46" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Validate Infrastructure and CMDB run spend baseline (record 41) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for it budget spend value.</x:v>
       </x:c>
       <x:c r="P46" t="str">
         <x:v>Medium</x:v>
@@ -2871,7 +2871,7 @@
         <x:v>CTO</x:v>
       </x:c>
       <x:c r="O47" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Confirm CMDB / infrastructure / cloud inventory context change / modernization budget (record 42) current-vs-target status, module boundary, volume baseline, and relationship links before this it budget spend value record is used downstream.</x:v>
       </x:c>
       <x:c r="P47" t="str">
         <x:v>Medium</x:v>
@@ -2921,7 +2921,7 @@
         <x:v>VP IT Operations</x:v>
       </x:c>
       <x:c r="O48" t="str">
-        <x:v>Actuals, forecast, capitalization policy, run/change split, and vendor allocation require validation.</x:v>
+        <x:v>Attach client evidence for Incident Problem Change Operations run spend baseline (record 43), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P48" t="str">
         <x:v>Medium</x:v>
@@ -2971,7 +2971,7 @@
         <x:v>VP IT Operations</x:v>
       </x:c>
       <x:c r="O49" t="str">
-        <x:v>Funding approval, benefit baseline, and delivery phasing require validation.</x:v>
+        <x:v>Reconcile Incident / problem / change operational health context change / modernization budget (record 44) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P49" t="str">
         <x:v>Medium</x:v>
@@ -3004,7 +3004,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R189b20bee8c748ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f57428c5942492a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3079,7 +3079,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6e49c31b8394c1b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ea0354662b34d54"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3271,7 +3271,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a4f1e100e424aca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R899ccfbe76a7485f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3365,7 +3365,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R286a561cbc3a4c2f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07d13db0c63b4d3b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3475,7 +3475,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb5adde3f65b4750"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0d8044ba8ab4f05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3583,7 +3583,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32254fc8d7d54b4f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56e6d3ac6fd44000"/>
   </x:tableParts>
 </x:worksheet>
 </file>